--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_2B59D18754BA3505AB592911591708F34BE7FA2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F3A7155-2FC9-47E2-8D43-F094B29FE496}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_2B59D18754CA3263BFD82411592628327845FB2A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9903EF5-734B-4D17-B39C-7B34CF412AD7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,16 +82,16 @@
     <t>14:00</t>
   </si>
   <si>
-    <t>EGYPT 1</t>
-  </si>
-  <si>
-    <t>Al Ahly Cairo x Smouha</t>
-  </si>
-  <si>
-    <t>Al Ahly Cairo</t>
-  </si>
-  <si>
-    <t>Smouha</t>
+    <t>TURKEY 2</t>
+  </si>
+  <si>
+    <t>Bursaspor x Istanbulspor</t>
+  </si>
+  <si>
+    <t>Bursaspor</t>
+  </si>
+  <si>
+    <t>Istanbulspor</t>
   </si>
   <si>
     <t>Lay Draw (Fav &lt;= 1.40)</t>
@@ -130,10 +130,10 @@
     <t>Match Odds (Home)</t>
   </si>
   <si>
-    <t>2x0</t>
-  </si>
-  <si>
-    <t>1x3</t>
+    <t>4x0</t>
+  </si>
+  <si>
+    <t>0x2</t>
   </si>
 </sst>
 </file>
@@ -584,13 +584,13 @@
         <v>26</v>
       </c>
       <c r="J2">
-        <v>5.0999999999999996</v>
+        <v>5.9</v>
       </c>
       <c r="K2">
         <v>1.4</v>
       </c>
       <c r="L2">
-        <v>24.39</v>
+        <v>20.41</v>
       </c>
       <c r="M2">
         <v>100</v>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,31 @@
           <t>PnL_R$</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte_Placar</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_stake_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Convencao_PnL</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Placar_Original</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado_Original</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -610,10 +635,33 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.95</v>
+        <v>0.19388</v>
       </c>
       <c r="T2" t="n">
         <v>19.39</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>betfair:fuzzy0.96</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4x0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -676,17 +724,15 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>0.95</v>
       </c>
@@ -695,11 +741,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T3" t="n">
-        <v>16.97</v>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
@@ -724,15 +724,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q3" t="n">
         <v>0.95</v>
       </c>
@@ -741,11 +743,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0.16964</v>
+      </c>
+      <c r="T3" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>0x2</t>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,31 +529,6 @@
           <t>PnL_R$</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte_Placar</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>PnL_stake_u</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Convencao_PnL</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Placar_Original</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Resultado_Original</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -635,33 +610,10 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.19388</v>
+        <v>0.95</v>
       </c>
       <c r="T2" t="n">
         <v>19.39</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>betfair:fuzzy0.96</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4x0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -744,33 +696,10 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.16964</v>
+        <v>0.95</v>
       </c>
       <c r="T3" t="n">
-        <v>16.96</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0x2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
+        <v>16.97</v>
       </c>
     </row>
   </sheetData>
